--- a/artfynd/A 22860-2026 artfynd.xlsx
+++ b/artfynd/A 22860-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ79"/>
+  <dimension ref="A1:AZ80"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -9426,10 +9426,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>118967313</v>
+        <v>137232600</v>
       </c>
       <c r="B72" t="n">
-        <v>58649</v>
+        <v>58680</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -9437,16 +9437,16 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>103057</v>
+        <v>103046</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Sävsparv</t>
+          <t>Gråsiska</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Emberiza schoeniclus</t>
+          <t>Acanthis flammea</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
@@ -9456,14 +9456,14 @@
       </c>
       <c r="I72" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>55</t>
         </is>
       </c>
       <c r="K72" t="inlineStr"/>
       <c r="L72" t="inlineStr"/>
       <c r="M72" t="inlineStr">
         <is>
-          <t>födosökande</t>
+          <t>sträckande S</t>
         </is>
       </c>
       <c r="N72" t="inlineStr"/>
@@ -9503,22 +9503,22 @@
       </c>
       <c r="Y72" t="inlineStr">
         <is>
-          <t>2024-08-07</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="Z72" t="inlineStr">
         <is>
-          <t>05:00</t>
+          <t>08:00</t>
         </is>
       </c>
       <c r="AA72" t="inlineStr">
         <is>
-          <t>2024-08-07</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="AB72" t="inlineStr">
         <is>
-          <t>08:00</t>
+          <t>10:00</t>
         </is>
       </c>
       <c r="AD72" t="b">
@@ -9544,16 +9544,16 @@
       <c r="AY72" t="inlineStr"/>
       <c r="AZ72" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/118967313</t>
+          <t>https://artportalen.se/Sighting/137232600</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>133262505</v>
+        <v>118967313</v>
       </c>
       <c r="B73" t="n">
-        <v>58671</v>
+        <v>58649</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -9580,30 +9580,30 @@
       </c>
       <c r="I73" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="K73" t="inlineStr"/>
       <c r="L73" t="inlineStr"/>
       <c r="M73" t="inlineStr">
         <is>
-          <t>spel/sång</t>
+          <t>födosökande</t>
         </is>
       </c>
       <c r="N73" t="inlineStr"/>
       <c r="P73" t="inlineStr">
         <is>
-          <t>Sandsjön, Vaggeryds k:n, Sm</t>
+          <t>Tornet,Sandsjön,Vaggeryd, Sm</t>
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>453157</v>
+        <v>453205</v>
       </c>
       <c r="R73" t="n">
-        <v>6377067</v>
+        <v>6377057</v>
       </c>
       <c r="S73" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T73" t="inlineStr">
         <is>
@@ -9627,22 +9627,22 @@
       </c>
       <c r="Y73" t="inlineStr">
         <is>
-          <t>2026-05-09</t>
+          <t>2024-08-07</t>
         </is>
       </c>
       <c r="Z73" t="inlineStr">
         <is>
-          <t>04:00</t>
+          <t>05:00</t>
         </is>
       </c>
       <c r="AA73" t="inlineStr">
         <is>
-          <t>2026-05-09</t>
+          <t>2024-08-07</t>
         </is>
       </c>
       <c r="AB73" t="inlineStr">
         <is>
-          <t>12:15</t>
+          <t>08:00</t>
         </is>
       </c>
       <c r="AD73" t="b">
@@ -9657,77 +9657,77 @@
       <c r="AT73" t="inlineStr"/>
       <c r="AW73" t="inlineStr">
         <is>
-          <t>Hans Boberg</t>
+          <t>Per-Arne Fransson</t>
         </is>
       </c>
       <c r="AX73" t="inlineStr">
         <is>
-          <t>Hans Boberg, Per-Arne Fransson, Per Landin, Andreas Ljung</t>
+          <t>Per-Arne Fransson</t>
         </is>
       </c>
       <c r="AY73" t="inlineStr"/>
       <c r="AZ73" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/133262505</t>
+          <t>https://artportalen.se/Sighting/118967313</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>132059774</v>
+        <v>133262505</v>
       </c>
       <c r="B74" t="n">
-        <v>57914</v>
+        <v>58671</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E74" t="n">
-        <v>103060</v>
+        <v>103057</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Brun glada</t>
+          <t>Sävsparv</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Milvus migrans</t>
+          <t>Emberiza schoeniclus</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Boddaert, 1783)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I74" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>5</t>
         </is>
       </c>
       <c r="K74" t="inlineStr"/>
       <c r="L74" t="inlineStr"/>
       <c r="M74" t="inlineStr">
         <is>
-          <t>sträckande N</t>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="N74" t="inlineStr"/>
       <c r="P74" t="inlineStr">
         <is>
-          <t>Tornet,Sandsjön,Vaggeryd, Sm</t>
+          <t>Sandsjön, Vaggeryds k:n, Sm</t>
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>453205</v>
+        <v>453157</v>
       </c>
       <c r="R74" t="n">
-        <v>6377057</v>
+        <v>6377067</v>
       </c>
       <c r="S74" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T74" t="inlineStr">
         <is>
@@ -9751,22 +9751,22 @@
       </c>
       <c r="Y74" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-05-09</t>
         </is>
       </c>
       <c r="Z74" t="inlineStr">
         <is>
-          <t>09:00</t>
+          <t>04:00</t>
         </is>
       </c>
       <c r="AA74" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-05-09</t>
         </is>
       </c>
       <c r="AB74" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>12:15</t>
         </is>
       </c>
       <c r="AD74" t="b">
@@ -9781,61 +9781,61 @@
       <c r="AT74" t="inlineStr"/>
       <c r="AW74" t="inlineStr">
         <is>
-          <t>Per-Arne Fransson</t>
+          <t>Hans Boberg</t>
         </is>
       </c>
       <c r="AX74" t="inlineStr">
         <is>
-          <t>Per-Arne Fransson</t>
+          <t>Hans Boberg, Per-Arne Fransson, Per Landin, Andreas Ljung</t>
         </is>
       </c>
       <c r="AY74" t="inlineStr"/>
       <c r="AZ74" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/132059774</t>
+          <t>https://artportalen.se/Sighting/133262505</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>119403340</v>
+        <v>132059774</v>
       </c>
       <c r="B75" t="n">
-        <v>57738</v>
+        <v>57914</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E75" t="n">
-        <v>205497</v>
+        <v>103060</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Ägretthäger</t>
+          <t>Brun glada</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Ardea alba</t>
+          <t>Milvus migrans</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Boddaert, 1783)</t>
         </is>
       </c>
       <c r="I75" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K75" t="inlineStr"/>
       <c r="L75" t="inlineStr"/>
       <c r="M75" t="inlineStr">
         <is>
-          <t>sträckande S</t>
+          <t>sträckande N</t>
         </is>
       </c>
       <c r="N75" t="inlineStr"/>
@@ -9875,17 +9875,17 @@
       </c>
       <c r="Y75" t="inlineStr">
         <is>
-          <t>2024-08-29</t>
+          <t>2026-03-31</t>
         </is>
       </c>
       <c r="Z75" t="inlineStr">
         <is>
-          <t>05:50</t>
+          <t>09:00</t>
         </is>
       </c>
       <c r="AA75" t="inlineStr">
         <is>
-          <t>2024-08-29</t>
+          <t>2026-03-31</t>
         </is>
       </c>
       <c r="AB75" t="inlineStr">
@@ -9916,16 +9916,16 @@
       <c r="AY75" t="inlineStr"/>
       <c r="AZ75" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/119403340</t>
+          <t>https://artportalen.se/Sighting/132059774</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>123949519</v>
+        <v>119403340</v>
       </c>
       <c r="B76" t="n">
-        <v>57572</v>
+        <v>57738</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -9933,16 +9933,16 @@
         </is>
       </c>
       <c r="E76" t="n">
-        <v>205660</v>
+        <v>205497</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Silltrut</t>
+          <t>Ägretthäger</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Larus fuscus</t>
+          <t>Ardea alba</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
@@ -9952,18 +9952,14 @@
       </c>
       <c r="I76" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K76" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="K76" t="inlineStr"/>
       <c r="L76" t="inlineStr"/>
       <c r="M76" t="inlineStr">
         <is>
-          <t>sträckande N</t>
+          <t>sträckande S</t>
         </is>
       </c>
       <c r="N76" t="inlineStr"/>
@@ -10003,27 +9999,22 @@
       </c>
       <c r="Y76" t="inlineStr">
         <is>
-          <t>2025-04-10</t>
+          <t>2024-08-29</t>
         </is>
       </c>
       <c r="Z76" t="inlineStr">
         <is>
-          <t>06:30</t>
+          <t>05:50</t>
         </is>
       </c>
       <c r="AA76" t="inlineStr">
         <is>
-          <t>2025-04-10</t>
+          <t>2024-08-29</t>
         </is>
       </c>
       <c r="AB76" t="inlineStr">
         <is>
-          <t>11:50</t>
-        </is>
-      </c>
-      <c r="AC76" t="inlineStr">
-        <is>
-          <t>med 6 Fiskmåsar</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AD76" t="b">
@@ -10049,33 +10040,33 @@
       <c r="AY76" t="inlineStr"/>
       <c r="AZ76" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/123949519</t>
+          <t>https://artportalen.se/Sighting/119403340</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>118967185</v>
+        <v>123949519</v>
       </c>
       <c r="B77" t="n">
-        <v>58085</v>
+        <v>57572</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E77" t="n">
-        <v>205976</v>
+        <v>205660</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Gråkråka</t>
+          <t>Silltrut</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Corvus corone cornix</t>
+          <t>Larus fuscus</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
@@ -10085,14 +10076,18 @@
       </c>
       <c r="I77" t="inlineStr">
         <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="K77" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K77" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
       <c r="L77" t="inlineStr"/>
       <c r="M77" t="inlineStr">
         <is>
-          <t>förbiflygande</t>
+          <t>sträckande N</t>
         </is>
       </c>
       <c r="N77" t="inlineStr"/>
@@ -10132,22 +10127,27 @@
       </c>
       <c r="Y77" t="inlineStr">
         <is>
-          <t>2024-08-07</t>
+          <t>2025-04-10</t>
         </is>
       </c>
       <c r="Z77" t="inlineStr">
         <is>
-          <t>05:00</t>
+          <t>06:30</t>
         </is>
       </c>
       <c r="AA77" t="inlineStr">
         <is>
-          <t>2024-08-07</t>
+          <t>2025-04-10</t>
         </is>
       </c>
       <c r="AB77" t="inlineStr">
         <is>
-          <t>08:00</t>
+          <t>11:50</t>
+        </is>
+      </c>
+      <c r="AC77" t="inlineStr">
+        <is>
+          <t>med 6 Fiskmåsar</t>
         </is>
       </c>
       <c r="AD77" t="b">
@@ -10173,16 +10173,16 @@
       <c r="AY77" t="inlineStr"/>
       <c r="AZ77" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/118967185</t>
+          <t>https://artportalen.se/Sighting/123949519</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>78986241</v>
+        <v>118967185</v>
       </c>
       <c r="B78" t="n">
-        <v>56884</v>
+        <v>58085</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -10190,34 +10190,33 @@
         </is>
       </c>
       <c r="E78" t="n">
-        <v>208255</v>
+        <v>205976</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Skogsödla</t>
+          <t>Gråkråka</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Zootoca vivipara</t>
+          <t>Corvus corone cornix</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(Jacquin, 1787)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I78" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J78" t="inlineStr"/>
+          <t>5</t>
+        </is>
+      </c>
       <c r="K78" t="inlineStr"/>
       <c r="L78" t="inlineStr"/>
       <c r="M78" t="inlineStr">
         <is>
-          <t>vilande</t>
+          <t>förbiflygande</t>
         </is>
       </c>
       <c r="N78" t="inlineStr"/>
@@ -10257,22 +10256,22 @@
       </c>
       <c r="Y78" t="inlineStr">
         <is>
-          <t>2019-07-19</t>
+          <t>2024-08-07</t>
         </is>
       </c>
       <c r="Z78" t="inlineStr">
         <is>
-          <t>10:30</t>
+          <t>05:00</t>
         </is>
       </c>
       <c r="AA78" t="inlineStr">
         <is>
-          <t>2019-07-19</t>
+          <t>2024-08-07</t>
         </is>
       </c>
       <c r="AB78" t="inlineStr">
         <is>
-          <t>10:30</t>
+          <t>08:00</t>
         </is>
       </c>
       <c r="AD78" t="b">
@@ -10281,7 +10280,6 @@
       <c r="AE78" t="b">
         <v>0</v>
       </c>
-      <c r="AF78" t="inlineStr"/>
       <c r="AG78" t="b">
         <v>0</v>
       </c>
@@ -10299,16 +10297,16 @@
       <c r="AY78" t="inlineStr"/>
       <c r="AZ78" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/78986241</t>
+          <t>https://artportalen.se/Sighting/118967185</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>86131648</v>
+        <v>78986241</v>
       </c>
       <c r="B79" t="n">
-        <v>45298</v>
+        <v>56884</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -10316,21 +10314,21 @@
         </is>
       </c>
       <c r="E79" t="n">
-        <v>208306</v>
+        <v>208255</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Bred kärrtrollslända</t>
+          <t>Skogsödla</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Leucorrhinia caudalis</t>
+          <t>Zootoca vivipara</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(Charpentier, 1840)</t>
+          <t>(Jacquin, 1787)</t>
         </is>
       </c>
       <c r="I79" t="inlineStr">
@@ -10339,11 +10337,7 @@
         </is>
       </c>
       <c r="J79" t="inlineStr"/>
-      <c r="K79" t="inlineStr">
-        <is>
-          <t>imago/adult</t>
-        </is>
-      </c>
+      <c r="K79" t="inlineStr"/>
       <c r="L79" t="inlineStr"/>
       <c r="M79" t="inlineStr">
         <is>
@@ -10353,17 +10347,17 @@
       <c r="N79" t="inlineStr"/>
       <c r="P79" t="inlineStr">
         <is>
-          <t>tornet, Sandsjön, Vaggeryds k:n, Sm</t>
+          <t>Tornet,Sandsjön,Vaggeryd, Sm</t>
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>453186</v>
+        <v>453205</v>
       </c>
       <c r="R79" t="n">
-        <v>6377118</v>
+        <v>6377057</v>
       </c>
       <c r="S79" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T79" t="inlineStr">
         <is>
@@ -10387,22 +10381,22 @@
       </c>
       <c r="Y79" t="inlineStr">
         <is>
-          <t>2020-06-08</t>
+          <t>2019-07-19</t>
         </is>
       </c>
       <c r="Z79" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>10:30</t>
         </is>
       </c>
       <c r="AA79" t="inlineStr">
         <is>
-          <t>2020-06-08</t>
+          <t>2019-07-19</t>
         </is>
       </c>
       <c r="AB79" t="inlineStr">
         <is>
-          <t>19:15</t>
+          <t>10:30</t>
         </is>
       </c>
       <c r="AD79" t="b">
@@ -10418,16 +10412,146 @@
       <c r="AT79" t="inlineStr"/>
       <c r="AW79" t="inlineStr">
         <is>
-          <t>Bo Andersson</t>
+          <t>Per-Arne Fransson</t>
         </is>
       </c>
       <c r="AX79" t="inlineStr">
         <is>
-          <t>Bo Andersson</t>
+          <t>Per-Arne Fransson</t>
         </is>
       </c>
       <c r="AY79" t="inlineStr"/>
       <c r="AZ79" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/78986241</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="n">
+        <v>86131648</v>
+      </c>
+      <c r="B80" t="n">
+        <v>45298</v>
+      </c>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E80" t="n">
+        <v>208306</v>
+      </c>
+      <c r="F80" t="inlineStr">
+        <is>
+          <t>Bred kärrtrollslända</t>
+        </is>
+      </c>
+      <c r="G80" t="inlineStr">
+        <is>
+          <t>Leucorrhinia caudalis</t>
+        </is>
+      </c>
+      <c r="H80" t="inlineStr">
+        <is>
+          <t>(Charpentier, 1840)</t>
+        </is>
+      </c>
+      <c r="I80" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J80" t="inlineStr"/>
+      <c r="K80" t="inlineStr">
+        <is>
+          <t>imago/adult</t>
+        </is>
+      </c>
+      <c r="L80" t="inlineStr"/>
+      <c r="M80" t="inlineStr">
+        <is>
+          <t>vilande</t>
+        </is>
+      </c>
+      <c r="N80" t="inlineStr"/>
+      <c r="P80" t="inlineStr">
+        <is>
+          <t>tornet, Sandsjön, Vaggeryds k:n, Sm</t>
+        </is>
+      </c>
+      <c r="Q80" t="n">
+        <v>453186</v>
+      </c>
+      <c r="R80" t="n">
+        <v>6377118</v>
+      </c>
+      <c r="S80" t="n">
+        <v>25</v>
+      </c>
+      <c r="T80" t="inlineStr">
+        <is>
+          <t>Jönköping</t>
+        </is>
+      </c>
+      <c r="U80" t="inlineStr">
+        <is>
+          <t>Vaggeryd</t>
+        </is>
+      </c>
+      <c r="V80" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W80" t="inlineStr">
+        <is>
+          <t>Byarum</t>
+        </is>
+      </c>
+      <c r="Y80" t="inlineStr">
+        <is>
+          <t>2020-06-08</t>
+        </is>
+      </c>
+      <c r="Z80" t="inlineStr">
+        <is>
+          <t>16:00</t>
+        </is>
+      </c>
+      <c r="AA80" t="inlineStr">
+        <is>
+          <t>2020-06-08</t>
+        </is>
+      </c>
+      <c r="AB80" t="inlineStr">
+        <is>
+          <t>19:15</t>
+        </is>
+      </c>
+      <c r="AD80" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE80" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF80" t="inlineStr"/>
+      <c r="AG80" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT80" t="inlineStr"/>
+      <c r="AW80" t="inlineStr">
+        <is>
+          <t>Bo Andersson</t>
+        </is>
+      </c>
+      <c r="AX80" t="inlineStr">
+        <is>
+          <t>Bo Andersson</t>
+        </is>
+      </c>
+      <c r="AY80" t="inlineStr"/>
+      <c r="AZ80" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/86131648</t>
         </is>
@@ -10513,6 +10637,7 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ77" r:id="rId76"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ78" r:id="rId77"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ79" r:id="rId78"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ80" r:id="rId79"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 22860-2026 artfynd.xlsx
+++ b/artfynd/A 22860-2026 artfynd.xlsx
@@ -9429,7 +9429,7 @@
         <v>137232600</v>
       </c>
       <c r="B72" t="n">
-        <v>58680</v>
+        <v>58682</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>

--- a/artfynd/A 22860-2026 artfynd.xlsx
+++ b/artfynd/A 22860-2026 artfynd.xlsx
@@ -9461,11 +9461,7 @@
       </c>
       <c r="K72" t="inlineStr"/>
       <c r="L72" t="inlineStr"/>
-      <c r="M72" t="inlineStr">
-        <is>
-          <t>sträckande S</t>
-        </is>
-      </c>
+      <c r="M72" t="inlineStr"/>
       <c r="N72" t="inlineStr"/>
       <c r="P72" t="inlineStr">
         <is>

--- a/artfynd/A 22860-2026 artfynd.xlsx
+++ b/artfynd/A 22860-2026 artfynd.xlsx
@@ -9429,7 +9429,7 @@
         <v>137232600</v>
       </c>
       <c r="B72" t="n">
-        <v>58682</v>
+        <v>58692</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>

--- a/artfynd/A 22860-2026 artfynd.xlsx
+++ b/artfynd/A 22860-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ80"/>
+  <dimension ref="A1:AZ81"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -8810,10 +8810,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>133262611</v>
+        <v>137322688</v>
       </c>
       <c r="B67" t="n">
-        <v>58104</v>
+        <v>58189</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -8821,26 +8821,26 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>103035</v>
+        <v>103023</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Kråka</t>
+          <t>Tofsmes</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Corvus corone</t>
+          <t>Lophophanes cristatus</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I67" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K67" t="inlineStr"/>
@@ -8849,17 +8849,17 @@
       <c r="N67" t="inlineStr"/>
       <c r="P67" t="inlineStr">
         <is>
-          <t>Sandsjön, Vaggeryds k:n, Sm</t>
+          <t>Tornet,Sandsjön,Vaggeryd, Sm</t>
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>453157</v>
+        <v>453205</v>
       </c>
       <c r="R67" t="n">
-        <v>6377067</v>
+        <v>6377057</v>
       </c>
       <c r="S67" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T67" t="inlineStr">
         <is>
@@ -8883,22 +8883,22 @@
       </c>
       <c r="Y67" t="inlineStr">
         <is>
-          <t>2026-05-09</t>
+          <t>2026-10-18</t>
         </is>
       </c>
       <c r="Z67" t="inlineStr">
         <is>
-          <t>04:00</t>
+          <t>08:15</t>
         </is>
       </c>
       <c r="AA67" t="inlineStr">
         <is>
-          <t>2026-05-09</t>
+          <t>2026-10-18</t>
         </is>
       </c>
       <c r="AB67" t="inlineStr">
         <is>
-          <t>12:15</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -8913,44 +8913,44 @@
       <c r="AT67" t="inlineStr"/>
       <c r="AW67" t="inlineStr">
         <is>
-          <t>Hans Boberg</t>
+          <t>Per-Arne Fransson</t>
         </is>
       </c>
       <c r="AX67" t="inlineStr">
         <is>
-          <t>Hans Boberg, Per-Arne Fransson, Per Landin, Andreas Ljung</t>
+          <t>Per-Arne Fransson</t>
         </is>
       </c>
       <c r="AY67" t="inlineStr"/>
       <c r="AZ67" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/133262611</t>
+          <t>https://artportalen.se/Sighting/137322688</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>123406104</v>
+        <v>133262611</v>
       </c>
       <c r="B68" t="n">
-        <v>58353</v>
+        <v>58104</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>103037</v>
+        <v>103035</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Stare</t>
+          <t>Kråka</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Sturnus vulgaris</t>
+          <t>Corvus corone</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
@@ -8960,30 +8960,26 @@
       </c>
       <c r="I68" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>20</t>
         </is>
       </c>
       <c r="K68" t="inlineStr"/>
       <c r="L68" t="inlineStr"/>
-      <c r="M68" t="inlineStr">
-        <is>
-          <t>sträckande N</t>
-        </is>
-      </c>
+      <c r="M68" t="inlineStr"/>
       <c r="N68" t="inlineStr"/>
       <c r="P68" t="inlineStr">
         <is>
-          <t>Tornet,Sandsjön,Vaggeryd, Sm</t>
+          <t>Sandsjön, Vaggeryds k:n, Sm</t>
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>453205</v>
+        <v>453157</v>
       </c>
       <c r="R68" t="n">
-        <v>6377057</v>
+        <v>6377067</v>
       </c>
       <c r="S68" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T68" t="inlineStr">
         <is>
@@ -9007,22 +9003,22 @@
       </c>
       <c r="Y68" t="inlineStr">
         <is>
-          <t>2025-03-23</t>
+          <t>2026-05-09</t>
         </is>
       </c>
       <c r="Z68" t="inlineStr">
         <is>
-          <t>06:00</t>
+          <t>04:00</t>
         </is>
       </c>
       <c r="AA68" t="inlineStr">
         <is>
-          <t>2025-03-23</t>
+          <t>2026-05-09</t>
         </is>
       </c>
       <c r="AB68" t="inlineStr">
         <is>
-          <t>11:30</t>
+          <t>12:15</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -9037,44 +9033,44 @@
       <c r="AT68" t="inlineStr"/>
       <c r="AW68" t="inlineStr">
         <is>
-          <t>Per-Arne Fransson</t>
+          <t>Hans Boberg</t>
         </is>
       </c>
       <c r="AX68" t="inlineStr">
         <is>
-          <t>Per-Arne Fransson</t>
+          <t>Hans Boberg, Per-Arne Fransson, Per Landin, Andreas Ljung</t>
         </is>
       </c>
       <c r="AY68" t="inlineStr"/>
       <c r="AZ68" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/123406104</t>
+          <t>https://artportalen.se/Sighting/133262611</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>132443990</v>
+        <v>123406104</v>
       </c>
       <c r="B69" t="n">
-        <v>58596</v>
+        <v>58353</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>103041</v>
+        <v>103037</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Bergfink</t>
+          <t>Stare</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Fringilla montifringilla</t>
+          <t>Sturnus vulgaris</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
@@ -9084,7 +9080,7 @@
       </c>
       <c r="I69" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>8</t>
         </is>
       </c>
       <c r="K69" t="inlineStr"/>
@@ -9131,22 +9127,22 @@
       </c>
       <c r="Y69" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2025-03-23</t>
         </is>
       </c>
       <c r="Z69" t="inlineStr">
         <is>
-          <t>06:15</t>
+          <t>06:00</t>
         </is>
       </c>
       <c r="AA69" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2025-03-23</t>
         </is>
       </c>
       <c r="AB69" t="inlineStr">
         <is>
-          <t>10:45</t>
+          <t>11:30</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -9172,50 +9168,50 @@
       <c r="AY69" t="inlineStr"/>
       <c r="AZ69" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/132443990</t>
+          <t>https://artportalen.se/Sighting/123406104</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>120060261</v>
+        <v>132443990</v>
       </c>
       <c r="B70" t="n">
-        <v>58602</v>
+        <v>58596</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>103042</v>
+        <v>103041</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Grönfink</t>
+          <t>Bergfink</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Chloris chloris</t>
+          <t>Fringilla montifringilla</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I70" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>15</t>
         </is>
       </c>
       <c r="K70" t="inlineStr"/>
       <c r="L70" t="inlineStr"/>
       <c r="M70" t="inlineStr">
         <is>
-          <t>sträckande S</t>
+          <t>sträckande N</t>
         </is>
       </c>
       <c r="N70" t="inlineStr"/>
@@ -9255,22 +9251,22 @@
       </c>
       <c r="Y70" t="inlineStr">
         <is>
-          <t>2024-09-28</t>
+          <t>2026-04-14</t>
         </is>
       </c>
       <c r="Z70" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>06:15</t>
         </is>
       </c>
       <c r="AA70" t="inlineStr">
         <is>
-          <t>2024-09-28</t>
+          <t>2026-04-14</t>
         </is>
       </c>
       <c r="AB70" t="inlineStr">
         <is>
-          <t>09:10</t>
+          <t>10:45</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -9296,33 +9292,33 @@
       <c r="AY70" t="inlineStr"/>
       <c r="AZ70" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/120060261</t>
+          <t>https://artportalen.se/Sighting/132443990</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>119369236</v>
+        <v>120060261</v>
       </c>
       <c r="B71" t="n">
-        <v>58636</v>
+        <v>58602</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E71" t="n">
-        <v>103044</v>
+        <v>103042</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Grönsiska</t>
+          <t>Grönfink</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Spinus spinus</t>
+          <t>Chloris chloris</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
@@ -9332,14 +9328,14 @@
       </c>
       <c r="I71" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="K71" t="inlineStr"/>
       <c r="L71" t="inlineStr"/>
       <c r="M71" t="inlineStr">
         <is>
-          <t>förbiflygande</t>
+          <t>sträckande S</t>
         </is>
       </c>
       <c r="N71" t="inlineStr"/>
@@ -9379,22 +9375,22 @@
       </c>
       <c r="Y71" t="inlineStr">
         <is>
-          <t>2024-08-27</t>
+          <t>2024-09-28</t>
         </is>
       </c>
       <c r="Z71" t="inlineStr">
         <is>
-          <t>06:00</t>
+          <t>07:20</t>
         </is>
       </c>
       <c r="AA71" t="inlineStr">
         <is>
-          <t>2024-08-27</t>
+          <t>2024-09-28</t>
         </is>
       </c>
       <c r="AB71" t="inlineStr">
         <is>
-          <t>11:45</t>
+          <t>09:10</t>
         </is>
       </c>
       <c r="AD71" t="b">
@@ -9420,16 +9416,16 @@
       <c r="AY71" t="inlineStr"/>
       <c r="AZ71" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/119369236</t>
+          <t>https://artportalen.se/Sighting/120060261</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>137232600</v>
+        <v>119369236</v>
       </c>
       <c r="B72" t="n">
-        <v>58692</v>
+        <v>58636</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -9437,16 +9433,16 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>103046</v>
+        <v>103044</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Gråsiska</t>
+          <t>Grönsiska</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Acanthis flammea</t>
+          <t>Spinus spinus</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
@@ -9456,12 +9452,16 @@
       </c>
       <c r="I72" t="inlineStr">
         <is>
-          <t>55</t>
+          <t>3</t>
         </is>
       </c>
       <c r="K72" t="inlineStr"/>
       <c r="L72" t="inlineStr"/>
-      <c r="M72" t="inlineStr"/>
+      <c r="M72" t="inlineStr">
+        <is>
+          <t>förbiflygande</t>
+        </is>
+      </c>
       <c r="N72" t="inlineStr"/>
       <c r="P72" t="inlineStr">
         <is>
@@ -9499,22 +9499,22 @@
       </c>
       <c r="Y72" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2024-08-27</t>
         </is>
       </c>
       <c r="Z72" t="inlineStr">
         <is>
-          <t>08:00</t>
+          <t>06:00</t>
         </is>
       </c>
       <c r="AA72" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2024-08-27</t>
         </is>
       </c>
       <c r="AB72" t="inlineStr">
         <is>
-          <t>10:00</t>
+          <t>11:45</t>
         </is>
       </c>
       <c r="AD72" t="b">
@@ -9540,16 +9540,16 @@
       <c r="AY72" t="inlineStr"/>
       <c r="AZ72" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137232600</t>
+          <t>https://artportalen.se/Sighting/119369236</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>118967313</v>
+        <v>137232600</v>
       </c>
       <c r="B73" t="n">
-        <v>58649</v>
+        <v>58692</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -9557,16 +9557,16 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>103057</v>
+        <v>103046</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Sävsparv</t>
+          <t>Gråsiska</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Emberiza schoeniclus</t>
+          <t>Acanthis flammea</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
@@ -9576,16 +9576,12 @@
       </c>
       <c r="I73" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>55</t>
         </is>
       </c>
       <c r="K73" t="inlineStr"/>
       <c r="L73" t="inlineStr"/>
-      <c r="M73" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
+      <c r="M73" t="inlineStr"/>
       <c r="N73" t="inlineStr"/>
       <c r="P73" t="inlineStr">
         <is>
@@ -9623,22 +9619,22 @@
       </c>
       <c r="Y73" t="inlineStr">
         <is>
-          <t>2024-08-07</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="Z73" t="inlineStr">
         <is>
-          <t>05:00</t>
+          <t>08:00</t>
         </is>
       </c>
       <c r="AA73" t="inlineStr">
         <is>
-          <t>2024-08-07</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="AB73" t="inlineStr">
         <is>
-          <t>08:00</t>
+          <t>10:00</t>
         </is>
       </c>
       <c r="AD73" t="b">
@@ -9664,16 +9660,16 @@
       <c r="AY73" t="inlineStr"/>
       <c r="AZ73" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/118967313</t>
+          <t>https://artportalen.se/Sighting/137232600</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>133262505</v>
+        <v>118967313</v>
       </c>
       <c r="B74" t="n">
-        <v>58671</v>
+        <v>58649</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -9700,30 +9696,30 @@
       </c>
       <c r="I74" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="K74" t="inlineStr"/>
       <c r="L74" t="inlineStr"/>
       <c r="M74" t="inlineStr">
         <is>
-          <t>spel/sång</t>
+          <t>födosökande</t>
         </is>
       </c>
       <c r="N74" t="inlineStr"/>
       <c r="P74" t="inlineStr">
         <is>
-          <t>Sandsjön, Vaggeryds k:n, Sm</t>
+          <t>Tornet,Sandsjön,Vaggeryd, Sm</t>
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>453157</v>
+        <v>453205</v>
       </c>
       <c r="R74" t="n">
-        <v>6377067</v>
+        <v>6377057</v>
       </c>
       <c r="S74" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T74" t="inlineStr">
         <is>
@@ -9747,22 +9743,22 @@
       </c>
       <c r="Y74" t="inlineStr">
         <is>
-          <t>2026-05-09</t>
+          <t>2024-08-07</t>
         </is>
       </c>
       <c r="Z74" t="inlineStr">
         <is>
-          <t>04:00</t>
+          <t>05:00</t>
         </is>
       </c>
       <c r="AA74" t="inlineStr">
         <is>
-          <t>2026-05-09</t>
+          <t>2024-08-07</t>
         </is>
       </c>
       <c r="AB74" t="inlineStr">
         <is>
-          <t>12:15</t>
+          <t>08:00</t>
         </is>
       </c>
       <c r="AD74" t="b">
@@ -9777,77 +9773,77 @@
       <c r="AT74" t="inlineStr"/>
       <c r="AW74" t="inlineStr">
         <is>
-          <t>Hans Boberg</t>
+          <t>Per-Arne Fransson</t>
         </is>
       </c>
       <c r="AX74" t="inlineStr">
         <is>
-          <t>Hans Boberg, Per-Arne Fransson, Per Landin, Andreas Ljung</t>
+          <t>Per-Arne Fransson</t>
         </is>
       </c>
       <c r="AY74" t="inlineStr"/>
       <c r="AZ74" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/133262505</t>
+          <t>https://artportalen.se/Sighting/118967313</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>132059774</v>
+        <v>133262505</v>
       </c>
       <c r="B75" t="n">
-        <v>57914</v>
+        <v>58671</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E75" t="n">
-        <v>103060</v>
+        <v>103057</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Brun glada</t>
+          <t>Sävsparv</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Milvus migrans</t>
+          <t>Emberiza schoeniclus</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Boddaert, 1783)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I75" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>5</t>
         </is>
       </c>
       <c r="K75" t="inlineStr"/>
       <c r="L75" t="inlineStr"/>
       <c r="M75" t="inlineStr">
         <is>
-          <t>sträckande N</t>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="N75" t="inlineStr"/>
       <c r="P75" t="inlineStr">
         <is>
-          <t>Tornet,Sandsjön,Vaggeryd, Sm</t>
+          <t>Sandsjön, Vaggeryds k:n, Sm</t>
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>453205</v>
+        <v>453157</v>
       </c>
       <c r="R75" t="n">
-        <v>6377057</v>
+        <v>6377067</v>
       </c>
       <c r="S75" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T75" t="inlineStr">
         <is>
@@ -9871,22 +9867,22 @@
       </c>
       <c r="Y75" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-05-09</t>
         </is>
       </c>
       <c r="Z75" t="inlineStr">
         <is>
-          <t>09:00</t>
+          <t>04:00</t>
         </is>
       </c>
       <c r="AA75" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-05-09</t>
         </is>
       </c>
       <c r="AB75" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>12:15</t>
         </is>
       </c>
       <c r="AD75" t="b">
@@ -9901,61 +9897,61 @@
       <c r="AT75" t="inlineStr"/>
       <c r="AW75" t="inlineStr">
         <is>
-          <t>Per-Arne Fransson</t>
+          <t>Hans Boberg</t>
         </is>
       </c>
       <c r="AX75" t="inlineStr">
         <is>
-          <t>Per-Arne Fransson</t>
+          <t>Hans Boberg, Per-Arne Fransson, Per Landin, Andreas Ljung</t>
         </is>
       </c>
       <c r="AY75" t="inlineStr"/>
       <c r="AZ75" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/132059774</t>
+          <t>https://artportalen.se/Sighting/133262505</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>119403340</v>
+        <v>132059774</v>
       </c>
       <c r="B76" t="n">
-        <v>57738</v>
+        <v>57914</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E76" t="n">
-        <v>205497</v>
+        <v>103060</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Ägretthäger</t>
+          <t>Brun glada</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Ardea alba</t>
+          <t>Milvus migrans</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Boddaert, 1783)</t>
         </is>
       </c>
       <c r="I76" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K76" t="inlineStr"/>
       <c r="L76" t="inlineStr"/>
       <c r="M76" t="inlineStr">
         <is>
-          <t>sträckande S</t>
+          <t>sträckande N</t>
         </is>
       </c>
       <c r="N76" t="inlineStr"/>
@@ -9995,17 +9991,17 @@
       </c>
       <c r="Y76" t="inlineStr">
         <is>
-          <t>2024-08-29</t>
+          <t>2026-03-31</t>
         </is>
       </c>
       <c r="Z76" t="inlineStr">
         <is>
-          <t>05:50</t>
+          <t>09:00</t>
         </is>
       </c>
       <c r="AA76" t="inlineStr">
         <is>
-          <t>2024-08-29</t>
+          <t>2026-03-31</t>
         </is>
       </c>
       <c r="AB76" t="inlineStr">
@@ -10036,16 +10032,16 @@
       <c r="AY76" t="inlineStr"/>
       <c r="AZ76" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/119403340</t>
+          <t>https://artportalen.se/Sighting/132059774</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>123949519</v>
+        <v>119403340</v>
       </c>
       <c r="B77" t="n">
-        <v>57572</v>
+        <v>57738</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -10053,16 +10049,16 @@
         </is>
       </c>
       <c r="E77" t="n">
-        <v>205660</v>
+        <v>205497</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Silltrut</t>
+          <t>Ägretthäger</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Larus fuscus</t>
+          <t>Ardea alba</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
@@ -10072,18 +10068,14 @@
       </c>
       <c r="I77" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K77" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="K77" t="inlineStr"/>
       <c r="L77" t="inlineStr"/>
       <c r="M77" t="inlineStr">
         <is>
-          <t>sträckande N</t>
+          <t>sträckande S</t>
         </is>
       </c>
       <c r="N77" t="inlineStr"/>
@@ -10123,27 +10115,22 @@
       </c>
       <c r="Y77" t="inlineStr">
         <is>
-          <t>2025-04-10</t>
+          <t>2024-08-29</t>
         </is>
       </c>
       <c r="Z77" t="inlineStr">
         <is>
-          <t>06:30</t>
+          <t>05:50</t>
         </is>
       </c>
       <c r="AA77" t="inlineStr">
         <is>
-          <t>2025-04-10</t>
+          <t>2024-08-29</t>
         </is>
       </c>
       <c r="AB77" t="inlineStr">
         <is>
-          <t>11:50</t>
-        </is>
-      </c>
-      <c r="AC77" t="inlineStr">
-        <is>
-          <t>med 6 Fiskmåsar</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AD77" t="b">
@@ -10169,33 +10156,33 @@
       <c r="AY77" t="inlineStr"/>
       <c r="AZ77" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/123949519</t>
+          <t>https://artportalen.se/Sighting/119403340</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>118967185</v>
+        <v>123949519</v>
       </c>
       <c r="B78" t="n">
-        <v>58085</v>
+        <v>57572</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E78" t="n">
-        <v>205976</v>
+        <v>205660</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Gråkråka</t>
+          <t>Silltrut</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Corvus corone cornix</t>
+          <t>Larus fuscus</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
@@ -10205,14 +10192,18 @@
       </c>
       <c r="I78" t="inlineStr">
         <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="K78" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K78" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
       <c r="L78" t="inlineStr"/>
       <c r="M78" t="inlineStr">
         <is>
-          <t>förbiflygande</t>
+          <t>sträckande N</t>
         </is>
       </c>
       <c r="N78" t="inlineStr"/>
@@ -10252,22 +10243,27 @@
       </c>
       <c r="Y78" t="inlineStr">
         <is>
-          <t>2024-08-07</t>
+          <t>2025-04-10</t>
         </is>
       </c>
       <c r="Z78" t="inlineStr">
         <is>
-          <t>05:00</t>
+          <t>06:30</t>
         </is>
       </c>
       <c r="AA78" t="inlineStr">
         <is>
-          <t>2024-08-07</t>
+          <t>2025-04-10</t>
         </is>
       </c>
       <c r="AB78" t="inlineStr">
         <is>
-          <t>08:00</t>
+          <t>11:50</t>
+        </is>
+      </c>
+      <c r="AC78" t="inlineStr">
+        <is>
+          <t>med 6 Fiskmåsar</t>
         </is>
       </c>
       <c r="AD78" t="b">
@@ -10293,16 +10289,16 @@
       <c r="AY78" t="inlineStr"/>
       <c r="AZ78" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/118967185</t>
+          <t>https://artportalen.se/Sighting/123949519</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>78986241</v>
+        <v>118967185</v>
       </c>
       <c r="B79" t="n">
-        <v>56884</v>
+        <v>58085</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -10310,34 +10306,33 @@
         </is>
       </c>
       <c r="E79" t="n">
-        <v>208255</v>
+        <v>205976</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Skogsödla</t>
+          <t>Gråkråka</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Zootoca vivipara</t>
+          <t>Corvus corone cornix</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(Jacquin, 1787)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I79" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J79" t="inlineStr"/>
+          <t>5</t>
+        </is>
+      </c>
       <c r="K79" t="inlineStr"/>
       <c r="L79" t="inlineStr"/>
       <c r="M79" t="inlineStr">
         <is>
-          <t>vilande</t>
+          <t>förbiflygande</t>
         </is>
       </c>
       <c r="N79" t="inlineStr"/>
@@ -10377,22 +10372,22 @@
       </c>
       <c r="Y79" t="inlineStr">
         <is>
-          <t>2019-07-19</t>
+          <t>2024-08-07</t>
         </is>
       </c>
       <c r="Z79" t="inlineStr">
         <is>
-          <t>10:30</t>
+          <t>05:00</t>
         </is>
       </c>
       <c r="AA79" t="inlineStr">
         <is>
-          <t>2019-07-19</t>
+          <t>2024-08-07</t>
         </is>
       </c>
       <c r="AB79" t="inlineStr">
         <is>
-          <t>10:30</t>
+          <t>08:00</t>
         </is>
       </c>
       <c r="AD79" t="b">
@@ -10401,7 +10396,6 @@
       <c r="AE79" t="b">
         <v>0</v>
       </c>
-      <c r="AF79" t="inlineStr"/>
       <c r="AG79" t="b">
         <v>0</v>
       </c>
@@ -10419,16 +10413,16 @@
       <c r="AY79" t="inlineStr"/>
       <c r="AZ79" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/78986241</t>
+          <t>https://artportalen.se/Sighting/118967185</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>86131648</v>
+        <v>78986241</v>
       </c>
       <c r="B80" t="n">
-        <v>45298</v>
+        <v>56884</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -10436,21 +10430,21 @@
         </is>
       </c>
       <c r="E80" t="n">
-        <v>208306</v>
+        <v>208255</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Bred kärrtrollslända</t>
+          <t>Skogsödla</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Leucorrhinia caudalis</t>
+          <t>Zootoca vivipara</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(Charpentier, 1840)</t>
+          <t>(Jacquin, 1787)</t>
         </is>
       </c>
       <c r="I80" t="inlineStr">
@@ -10459,11 +10453,7 @@
         </is>
       </c>
       <c r="J80" t="inlineStr"/>
-      <c r="K80" t="inlineStr">
-        <is>
-          <t>imago/adult</t>
-        </is>
-      </c>
+      <c r="K80" t="inlineStr"/>
       <c r="L80" t="inlineStr"/>
       <c r="M80" t="inlineStr">
         <is>
@@ -10473,17 +10463,17 @@
       <c r="N80" t="inlineStr"/>
       <c r="P80" t="inlineStr">
         <is>
-          <t>tornet, Sandsjön, Vaggeryds k:n, Sm</t>
+          <t>Tornet,Sandsjön,Vaggeryd, Sm</t>
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>453186</v>
+        <v>453205</v>
       </c>
       <c r="R80" t="n">
-        <v>6377118</v>
+        <v>6377057</v>
       </c>
       <c r="S80" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T80" t="inlineStr">
         <is>
@@ -10507,22 +10497,22 @@
       </c>
       <c r="Y80" t="inlineStr">
         <is>
-          <t>2020-06-08</t>
+          <t>2019-07-19</t>
         </is>
       </c>
       <c r="Z80" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>10:30</t>
         </is>
       </c>
       <c r="AA80" t="inlineStr">
         <is>
-          <t>2020-06-08</t>
+          <t>2019-07-19</t>
         </is>
       </c>
       <c r="AB80" t="inlineStr">
         <is>
-          <t>19:15</t>
+          <t>10:30</t>
         </is>
       </c>
       <c r="AD80" t="b">
@@ -10538,16 +10528,146 @@
       <c r="AT80" t="inlineStr"/>
       <c r="AW80" t="inlineStr">
         <is>
-          <t>Bo Andersson</t>
+          <t>Per-Arne Fransson</t>
         </is>
       </c>
       <c r="AX80" t="inlineStr">
         <is>
-          <t>Bo Andersson</t>
+          <t>Per-Arne Fransson</t>
         </is>
       </c>
       <c r="AY80" t="inlineStr"/>
       <c r="AZ80" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/78986241</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="n">
+        <v>86131648</v>
+      </c>
+      <c r="B81" t="n">
+        <v>45298</v>
+      </c>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E81" t="n">
+        <v>208306</v>
+      </c>
+      <c r="F81" t="inlineStr">
+        <is>
+          <t>Bred kärrtrollslända</t>
+        </is>
+      </c>
+      <c r="G81" t="inlineStr">
+        <is>
+          <t>Leucorrhinia caudalis</t>
+        </is>
+      </c>
+      <c r="H81" t="inlineStr">
+        <is>
+          <t>(Charpentier, 1840)</t>
+        </is>
+      </c>
+      <c r="I81" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J81" t="inlineStr"/>
+      <c r="K81" t="inlineStr">
+        <is>
+          <t>imago/adult</t>
+        </is>
+      </c>
+      <c r="L81" t="inlineStr"/>
+      <c r="M81" t="inlineStr">
+        <is>
+          <t>vilande</t>
+        </is>
+      </c>
+      <c r="N81" t="inlineStr"/>
+      <c r="P81" t="inlineStr">
+        <is>
+          <t>tornet, Sandsjön, Vaggeryds k:n, Sm</t>
+        </is>
+      </c>
+      <c r="Q81" t="n">
+        <v>453186</v>
+      </c>
+      <c r="R81" t="n">
+        <v>6377118</v>
+      </c>
+      <c r="S81" t="n">
+        <v>25</v>
+      </c>
+      <c r="T81" t="inlineStr">
+        <is>
+          <t>Jönköping</t>
+        </is>
+      </c>
+      <c r="U81" t="inlineStr">
+        <is>
+          <t>Vaggeryd</t>
+        </is>
+      </c>
+      <c r="V81" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W81" t="inlineStr">
+        <is>
+          <t>Byarum</t>
+        </is>
+      </c>
+      <c r="Y81" t="inlineStr">
+        <is>
+          <t>2020-06-08</t>
+        </is>
+      </c>
+      <c r="Z81" t="inlineStr">
+        <is>
+          <t>16:00</t>
+        </is>
+      </c>
+      <c r="AA81" t="inlineStr">
+        <is>
+          <t>2020-06-08</t>
+        </is>
+      </c>
+      <c r="AB81" t="inlineStr">
+        <is>
+          <t>19:15</t>
+        </is>
+      </c>
+      <c r="AD81" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE81" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF81" t="inlineStr"/>
+      <c r="AG81" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT81" t="inlineStr"/>
+      <c r="AW81" t="inlineStr">
+        <is>
+          <t>Bo Andersson</t>
+        </is>
+      </c>
+      <c r="AX81" t="inlineStr">
+        <is>
+          <t>Bo Andersson</t>
+        </is>
+      </c>
+      <c r="AY81" t="inlineStr"/>
+      <c r="AZ81" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/86131648</t>
         </is>
@@ -10634,6 +10754,7 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ78" r:id="rId77"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ79" r:id="rId78"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ80" r:id="rId79"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ81" r:id="rId80"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 22860-2026 artfynd.xlsx
+++ b/artfynd/A 22860-2026 artfynd.xlsx
@@ -8813,7 +8813,7 @@
         <v>137322688</v>
       </c>
       <c r="B67" t="n">
-        <v>58189</v>
+        <v>58190</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -9549,7 +9549,7 @@
         <v>137232600</v>
       </c>
       <c r="B73" t="n">
-        <v>58692</v>
+        <v>58694</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>

--- a/artfynd/A 22860-2026 artfynd.xlsx
+++ b/artfynd/A 22860-2026 artfynd.xlsx
@@ -8813,7 +8813,7 @@
         <v>137322688</v>
       </c>
       <c r="B67" t="n">
-        <v>58190</v>
+        <v>58191</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -9549,7 +9549,7 @@
         <v>137232600</v>
       </c>
       <c r="B73" t="n">
-        <v>58694</v>
+        <v>58696</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>

--- a/artfynd/A 22860-2026 artfynd.xlsx
+++ b/artfynd/A 22860-2026 artfynd.xlsx
@@ -8813,7 +8813,7 @@
         <v>137322688</v>
       </c>
       <c r="B67" t="n">
-        <v>58191</v>
+        <v>58194</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -9549,7 +9549,7 @@
         <v>137232600</v>
       </c>
       <c r="B73" t="n">
-        <v>58696</v>
+        <v>58699</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
